--- a/business_surveys/012_weekly_delivery_preferences_survey--business_surveys.xlsx
+++ b/business_surveys/012_weekly_delivery_preferences_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1126,17 +1126,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>delivery_instructions_1_choices</t>
+          <t>time_windows_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other_(_specify_below_)</t>
+          <t>7:00_am_-_8:00_am</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other ( specify below )</t>
+          <t>7:00 AM - 8:00 AM</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7:00_am_-_8:00_am</t>
+          <t>8:00_am_-_9:00_am</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7:00 AM - 8:00 AM</t>
+          <t>8:00 AM - 9:00 AM</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8:00_am_-_9:00_am</t>
+          <t>9:00_am_-_10:00_am</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8:00 AM - 9:00 AM</t>
+          <t>9:00 AM - 10:00 AM</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9:00_am_-_10:00_am</t>
+          <t>10:00_am_-_11:00_am</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9:00 AM - 10:00 AM</t>
+          <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:00_am_-_11:00_am</t>
+          <t>11:00_am_-_12:00_pm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10:00 AM - 11:00 AM</t>
+          <t>11:00 AM - 12:00 PM</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00_am_-_12:00_pm</t>
+          <t>12:00_pm_-_1:00_pm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11:00 AM - 12:00 PM</t>
+          <t>12:00 PM - 1:00 PM</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:00_pm_-_1:00_pm</t>
+          <t>1:00_pm_-_2:00_pm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12:00 PM - 1:00 PM</t>
+          <t>1:00 PM - 2:00 PM</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1:00_pm_-_2:00_pm</t>
+          <t>2:00_pm_-_3:00_pm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1:00 PM - 2:00 PM</t>
+          <t>2:00 PM - 3:00 PM</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2:00_pm_-_3:00_pm</t>
+          <t>3:00_pm_-_4:00_pm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2:00 PM - 3:00 PM</t>
+          <t>3:00 PM - 4:00 PM</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3:00_pm_-_4:00_pm</t>
+          <t>4:00_pm_-_5:00_pm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3:00 PM - 4:00 PM</t>
+          <t>4:00 PM - 5:00 PM</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4:00_pm_-_5:00_pm</t>
+          <t>5:00_pm_-_6:00_pm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4:00 PM - 5:00 PM</t>
+          <t>5:00 PM - 6:00 PM</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5:00_pm_-_6:00_pm</t>
+          <t>6:00_pm_-_7:00_pm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5:00 PM - 6:00 PM</t>
+          <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6:00_pm_-_7:00_pm</t>
+          <t>7:00_pm_-_8:00_pm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6:00 PM - 7:00 PM</t>
+          <t>7:00 PM - 8:00 PM</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7:00_pm_-_8:00_pm</t>
+          <t>8:00_pm_-_9:00_pm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7:00 PM - 8:00 PM</t>
+          <t>8:00 PM - 9:00 PM</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8:00_pm_-_9:00_pm</t>
+          <t>9:00_pm_-_10:00_pm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8:00 PM - 9:00 PM</t>
+          <t>9:00 PM - 10:00 PM</t>
         </is>
       </c>
     </row>
@@ -1386,27 +1386,10 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9:00_pm_-_10:00_pm</t>
+          <t>10:00_pm_-_11:00_pm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
-        <is>
-          <t>9:00 PM - 10:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>time_windows_2_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10:00_pm_-_11:00_pm</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>10:00 PM - 11:00 PM</t>
         </is>
